--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_89_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_89_R9.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1536</v>
+        <v>7.0058</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3549</v>
+        <v>4.6809</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7987</v>
+        <v>2.3249</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0223</v>
+        <v>1.1172</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6614</v>
+        <v>-0.6529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6391</v>
+        <v>1.77</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4328</v>
+        <v>2.3867</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1078</v>
+        <v>0.1918</v>
       </c>
       <c r="L2" t="n">
-        <v>1.325</v>
+        <v>2.1949</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4551</v>
+        <v>-1.2695</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7692</v>
+        <v>-0.8447</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6859</v>
+        <v>-0.4248</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>4.266</v>
+        <v>1.4969</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5637</v>
+        <v>0.3817</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7023</v>
+        <v>1.1152</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7501</v>
+        <v>1.6083</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7501</v>
+        <v>2.1444</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8599</v>
+        <v>4.813</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5014</v>
+        <v>2.5856</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3585</v>
+        <v>2.2274</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1172</v>
+        <v>-0.0223</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6529</v>
+        <v>-0.6614</v>
       </c>
       <c r="I3" t="n">
-        <v>1.77</v>
+        <v>0.6391</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3867</v>
+        <v>1.4328</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1918</v>
+        <v>0.1078</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1949</v>
+        <v>1.325</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2695</v>
+        <v>-1.4551</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8447</v>
+        <v>-0.7692</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4248</v>
+        <v>-0.6859</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.351</v>
+        <v>1.9254</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7978</v>
+        <v>0.7945</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1488</v>
+        <v>1.131</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6083</v>
+        <v>1.7501</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7982</v>
+        <v>1.9998</v>
       </c>
       <c r="E4" t="n">
         <v>0.4658</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3324</v>
+        <v>1.534</v>
       </c>
       <c r="G4" t="n">
         <v>1.037</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3901</v>
+        <v>0.5917</v>
       </c>
       <c r="T4" t="n">
         <v>0.1221</v>
       </c>
       <c r="U4" t="n">
-        <v>0.268</v>
+        <v>0.4696</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7886</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4129</v>
+        <v>1.5531</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1618</v>
+        <v>1.4016</v>
       </c>
       <c r="F5" t="n">
-        <v>1.251</v>
+        <v>0.1515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6331</v>
+        <v>-0.3658</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1766</v>
+        <v>-1.4633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8097</v>
+        <v>1.0975</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6371</v>
+        <v>-0.1439</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2457</v>
+        <v>-0.7695</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3914</v>
+        <v>0.6257</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.004</v>
+        <v>-0.222</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4223</v>
+        <v>-0.6938</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4183</v>
+        <v>0.4718</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1715</v>
+        <v>-0.1533</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8442</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3273</v>
+        <v>-0.0905</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1827</v>
+        <v>0.5477</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1657</v>
+        <v>0.8983</v>
       </c>
       <c r="F6" t="n">
-        <v>0.017</v>
+        <v>-0.3506</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3658</v>
+        <v>-0.1067</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4633</v>
+        <v>0.1141</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0975</v>
+        <v>-0.2208</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1439</v>
+        <v>1.3053</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7695</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6257</v>
+        <v>0.465</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.222</v>
+        <v>-1.412</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6938</v>
+        <v>-0.7261</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4718</v>
+        <v>-0.6859</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5236</v>
+        <v>0.6723</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>0.3068</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2249</v>
+        <v>0.3655</v>
       </c>
       <c r="V6" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8214</v>
+        <v>0.4569</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5985</v>
+        <v>-1.5248</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4199</v>
+        <v>1.9817</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.747</v>
+        <v>1.654</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5534</v>
+        <v>0.299</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8064</v>
+        <v>1.355</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7106</v>
+        <v>3.1414</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7842</v>
+        <v>1.4151</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0736</v>
+        <v>1.7263</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0364</v>
+        <v>-1.4874</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7692</v>
+        <v>-1.1161</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7328</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5863</v>
+        <v>1.1224</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0578</v>
+        <v>0.2047</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5285</v>
+        <v>0.9177</v>
       </c>
       <c r="V7" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6585</v>
+        <v>0.4356</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5248</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1834</v>
+        <v>1.2174</v>
       </c>
       <c r="G8" t="n">
-        <v>1.654</v>
+        <v>0.6331</v>
       </c>
       <c r="H8" t="n">
-        <v>0.299</v>
+        <v>-0.1766</v>
       </c>
       <c r="I8" t="n">
-        <v>1.355</v>
+        <v>0.8097</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1414</v>
+        <v>0.6371</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4151</v>
+        <v>0.2457</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7263</v>
+        <v>0.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4874</v>
+        <v>-0.004</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1161</v>
+        <v>-0.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3713</v>
+        <v>0.4183</v>
       </c>
       <c r="P8" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-2.3195</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-4.871</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3241</v>
+        <v>1.1942</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2047</v>
+        <v>0.9006</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1193</v>
+        <v>0.2937</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3109</v>
+        <v>0.2995</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3085</v>
+        <v>-0.9524</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6195000000000001</v>
+        <v>1.2519</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1067</v>
+        <v>-1.747</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1141</v>
+        <v>-2.5534</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2208</v>
+        <v>0.8064</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3053</v>
+        <v>-1.7106</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8401999999999999</v>
+        <v>-1.7842</v>
       </c>
       <c r="L9" t="n">
-        <v>0.465</v>
+        <v>0.0736</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.412</v>
+        <v>-0.0364</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7261</v>
+        <v>-0.7692</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>0.7328</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1863</v>
+        <v>1.0644</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2829</v>
+        <v>0.704</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.3605</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7568</v>
+        <v>-1.1442</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2187</v>
+        <v>-1.5726</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4619</v>
+        <v>0.4283</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5926</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6734</v>
+        <v>0.286</v>
       </c>
       <c r="T10" t="n">
-        <v>0.637</v>
+        <v>0.2831</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.438</v>
+        <v>-2.0677</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.519</v>
+        <v>-2.2831</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0809</v>
+        <v>0.2154</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2161</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.228</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.602</v>
+        <v>-4.12</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.9099</v>
+        <v>-6.7304</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3079</v>
+        <v>2.6104</v>
       </c>
       <c r="G12" t="n">
         <v>-5.8453</v>
@@ -1390,13 +1390,13 @@
         <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.09710000000000001</v>
+        <v>1.3849</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7231</v>
+        <v>0.4564</v>
       </c>
       <c r="U12" t="n">
-        <v>0.626</v>
+        <v>0.9285</v>
       </c>
       <c r="V12" t="n">
         <v>2.428</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.779500000000004</v>
+        <v>9.779499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.812800000000002</v>
+        <v>-3.812899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13.5921</v>
+        <v>13.5923</v>
       </c>
       <c r="G13" t="n">
         <v>-4.4545</v>
@@ -1444,7 +1444,7 @@
         <v>3.002799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7103</v>
+        <v>-0.7102999999999998</v>
       </c>
       <c r="L13" t="n">
         <v>3.7132</v>
@@ -1456,7 +1456,7 @@
         <v>-7.692099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2349000000000002</v>
+        <v>0.2349000000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-3.4794</v>
@@ -1468,13 +1468,13 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>9.357099999999999</v>
+        <v>9.3569</v>
       </c>
       <c r="T13" t="n">
         <v>3.9536</v>
       </c>
       <c r="U13" t="n">
-        <v>5.4035</v>
+        <v>5.4036</v>
       </c>
       <c r="V13" t="n">
         <v>8.356200000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.4441</v>
+        <v>4.4789</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9775</v>
+        <v>2.0339</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4666</v>
+        <v>2.4451</v>
       </c>
       <c r="G14" t="n">
         <v>4.7564</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5975</v>
+        <v>-0.3677</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5272</v>
+        <v>-0.4165</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0703</v>
+        <v>0.0488</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8506</v>
+        <v>1.0358</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0605</v>
+        <v>-0.2933</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7901</v>
+        <v>1.3291</v>
       </c>
       <c r="G15" t="n">
         <v>0.3444</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1896</v>
+        <v>-1.0045</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0351</v>
+        <v>-0.389</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1545</v>
+        <v>-0.6155</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3193</v>
+        <v>-0.5399</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2454</v>
+        <v>-2.6352</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9261</v>
+        <v>2.0953</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-1.9646</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1595</v>
+        <v>-1.0444</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5386</v>
+        <v>-0.9201</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0153</v>
+        <v>-1.3461</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4804</v>
+        <v>-1.0616</v>
       </c>
       <c r="L16" t="n">
-        <v>0.465</v>
+        <v>-0.2845</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6828</v>
+        <v>-0.6185</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3209</v>
+        <v>0.0171</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0037</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>3.4793</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.0154</v>
+        <v>3.4793</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4046</v>
+        <v>-1.771</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0703</v>
+        <v>-1.2891</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3343</v>
+        <v>-0.4819</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7016</v>
+        <v>-0.8298</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.9891</v>
+        <v>-1.8352</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2874</v>
+        <v>1.0054</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9646</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0444</v>
+        <v>-0.1595</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9201</v>
+        <v>-0.5386</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3461</v>
+        <v>-0.0153</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0616</v>
+        <v>-0.4804</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2845</v>
+        <v>0.465</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6185</v>
+        <v>-0.6828</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0171</v>
+        <v>0.3209</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.0037</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4793</v>
+        <v>1.8556</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>3.4793</v>
+        <v>3.0154</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.9328</v>
+        <v>-0.9151</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.643</v>
+        <v>-0.6601</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2898</v>
+        <v>-0.255</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8575</v>
+        <v>-0.9932</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3419</v>
+        <v>-0.8701</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.1231</v>
       </c>
       <c r="G18" t="n">
         <v>4.6789</v>
@@ -1858,13 +1858,13 @@
         <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4668</v>
+        <v>-0.6025</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2696</v>
+        <v>-0.7978</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1972</v>
+        <v>0.1953</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2862</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5536</v>
+        <v>-2.1984</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5075</v>
+        <v>-3.0006</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0461</v>
+        <v>0.8022</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0494</v>
+        <v>3.0392</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6111</v>
+        <v>2.3131</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4384</v>
+        <v>0.7262</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0594</v>
+        <v>2.5855</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2534</v>
+        <v>1.9598</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1939</v>
+        <v>0.6257</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.99</v>
+        <v>0.4537</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3577</v>
+        <v>0.3532</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6323</v>
+        <v>0.1005</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>3.4793</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1278</v>
+        <v>-1.7917</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3203</v>
+        <v>-0.8445</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5789</v>
+        <v>-2.6037</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4724</v>
+        <v>-1.3896</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1065</v>
+        <v>-1.2141</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0392</v>
+        <v>-2.0494</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3131</v>
+        <v>-1.6111</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7262</v>
+        <v>-0.4384</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5855</v>
+        <v>-1.0594</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9598</v>
+        <v>-1.2534</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6257</v>
+        <v>0.1939</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4537</v>
+        <v>-0.99</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3532</v>
+        <v>-0.3577</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1005</v>
+        <v>-0.6323</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.4793</v>
+        <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.1722</v>
+        <v>-0.1779</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.4189</v>
+        <v>-0.3301</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.7532</v>
+        <v>0.1522</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0632</v>
+        <v>-5.7702</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.074</v>
+        <v>-5.6022</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0108</v>
+        <v>-0.168</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6524</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6607</v>
+        <v>-0.3677</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.5737</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3848</v>
+        <v>0.206</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7501</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.779399999999999</v>
+        <v>-7.420499999999998</v>
       </c>
       <c r="E22" t="n">
         <v>-13.5923</v>
       </c>
       <c r="F22" t="n">
-        <v>3.8128</v>
+        <v>6.171900000000001</v>
       </c>
       <c r="G22" t="n">
         <v>4.4544</v>
@@ -2155,7 +2155,7 @@
         <v>-3.003</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7101999999999999</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-3.7132</v>
@@ -2170,13 +2170,13 @@
         <v>20.8758</v>
       </c>
       <c r="S22" t="n">
-        <v>-9.356999999999999</v>
+        <v>-6.998099999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.4033</v>
+        <v>-5.4034</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.953600000000001</v>
+        <v>-1.5946</v>
       </c>
       <c r="V22" t="n">
         <v>-8.356200000000001</v>
